--- a/details.xlsx
+++ b/details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wamp\www\web-development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6A5EFB-B9DB-47DA-9D60-D7DA9DFD2760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F275C0-619E-45CB-AD47-FC55B0C4A98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI-UX Components" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Create a script for to convert webp, avif and adding watermark. </t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>should show html content, links, small images, links should be clickable</t>
+  </si>
+  <si>
+    <t>user journey</t>
+  </si>
+  <si>
+    <t>when user land on home page and navigate several pages after filling the form we should get the user jouney in the form. User journey is created using session storage</t>
   </si>
 </sst>
 </file>
@@ -104,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -112,6 +118,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,11 +451,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4E557C-A5C3-4CD1-A1FE-4E2508118148}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.140625" customWidth="1"/>
-    <col min="2" max="2" width="60.42578125" customWidth="1"/>
+    <col min="1" max="1" width="66.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="60.42578125" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -473,6 +481,14 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/details.xlsx
+++ b/details.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wamp\www\web-development\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F275C0-619E-45CB-AD47-FC55B0C4A98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB5B44F-28FB-471C-92C6-367B59165769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI-UX Components" sheetId="1" r:id="rId1"/>
     <sheet name="Web Components" sheetId="2" r:id="rId2"/>
+    <sheet name="Form Components" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Create a script for to convert webp, avif and adding watermark. </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>load more products</t>
   </si>
@@ -68,6 +66,51 @@
   </si>
   <si>
     <t>when user land on home page and navigate several pages after filling the form we should get the user jouney in the form. User journey is created using session storage</t>
+  </si>
+  <si>
+    <t>slider</t>
+  </si>
+  <si>
+    <t>slick slider is best, customize that and use that so never need to update</t>
+  </si>
+  <si>
+    <t>sidebar stick</t>
+  </si>
+  <si>
+    <t>theia sticky</t>
+  </si>
+  <si>
+    <t>range slider</t>
+  </si>
+  <si>
+    <t>radio button</t>
+  </si>
+  <si>
+    <t>checkboxes</t>
+  </si>
+  <si>
+    <t>file uploading</t>
+  </si>
+  <si>
+    <t>select dropdown</t>
+  </si>
+  <si>
+    <t>watermark</t>
+  </si>
+  <si>
+    <t>Create a script for to convert webp</t>
+  </si>
+  <si>
+    <t>I want to create a watermark script in PHP.
+Source folder: this folder will be used to keep original images.
+Destination folder: this folder will be used to keep new watermarked images.
+The source file must remain the same; a new image should be created with a watermark.
+The script must be able to watermark jpg/png/webp image types without losing the quality.
+Use GD library.
+The new image name must be in lowercase, convert multiple spaces to one space, and then replace spaces with "-" dash. remove special characters.
+it should work for nested folder (having images) also.
+always replace the image if already exist.
+Apply watermark center center always.</t>
   </si>
 </sst>
 </file>
@@ -110,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -118,7 +161,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.5703125" style="1" customWidth="1"/>
@@ -409,39 +451,60 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -451,42 +514,79 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4E557C-A5C3-4CD1-A1FE-4E2508118148}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="60.42578125" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="66.140625" customWidth="1"/>
+    <col min="2" max="2" width="135.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
+    </row>
+    <row r="5" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D2AF4A-C400-45EA-8324-502FC26E439C}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
